--- a/request_forms/024_wallpaper_request_for_browser_extension--request_forms.xlsx
+++ b/request_forms/024_wallpaper_request_for_browser_extension--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'browser_extension'}</t>
+          <t>browser_extension</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Browser Extension'}</t>
+          <t>Browser Extension</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mobile_app'}</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mobile App'}</t>
+          <t>Mobile App</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'web_app'}</t>
+          <t>web_app</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Web App'}</t>
+          <t>Web App</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
